--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.69611612728195</v>
+        <v>8.725618870683316</v>
       </c>
       <c r="D2" t="n">
-        <v>52.44072202906594</v>
+        <v>8.521617329723215</v>
       </c>
       <c r="E2" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F2" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.82151641393875</v>
+        <v>8.258496417265047</v>
       </c>
       <c r="D3" t="n">
-        <v>51.35188157873412</v>
+        <v>8.344680756544296</v>
       </c>
       <c r="E3" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F3" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.69751550176233</v>
+        <v>6.775846269036379</v>
       </c>
       <c r="D4" t="n">
-        <v>40.57819023709546</v>
+        <v>6.593955913528013</v>
       </c>
       <c r="E4" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F4" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.01648351187345</v>
+        <v>5.365178570679436</v>
       </c>
       <c r="D5" t="n">
-        <v>31.62204231416522</v>
+        <v>5.138581876051848</v>
       </c>
       <c r="E5" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F5" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.1513004299672</v>
+        <v>4.249586319869671</v>
       </c>
       <c r="D6" t="n">
-        <v>26.34611879425695</v>
+        <v>4.281244304066754</v>
       </c>
       <c r="E6" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F6" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.74622183991916</v>
+        <v>3.533761048986863</v>
       </c>
       <c r="D7" t="n">
-        <v>20.39739769399645</v>
+        <v>3.314577125274423</v>
       </c>
       <c r="E7" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F7" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.00109015680696</v>
+        <v>4.22517715048113</v>
       </c>
       <c r="D8" t="n">
-        <v>53.13404389314167</v>
+        <v>8.634282132635521</v>
       </c>
       <c r="E8" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F8" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.98333758105617</v>
+        <v>2.922292356921627</v>
       </c>
       <c r="D9" t="n">
-        <v>18.02659440361245</v>
+        <v>2.929321590587024</v>
       </c>
       <c r="E9" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F9" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.57578864970771</v>
+        <v>3.993565655577504</v>
       </c>
       <c r="D10" t="n">
-        <v>31.96460648658003</v>
+        <v>5.194248554069256</v>
       </c>
       <c r="E10" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F10" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.04097587674143</v>
+        <v>6.019158579970482</v>
       </c>
       <c r="D11" t="n">
-        <v>36.90359149578528</v>
+        <v>5.996833618065108</v>
       </c>
       <c r="E11" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F11" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.49972319075065</v>
+        <v>3.168705018496981</v>
       </c>
       <c r="D12" t="n">
-        <v>18.38124319817949</v>
+        <v>2.986952019704167</v>
       </c>
       <c r="E12" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F12" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5.337714211369902</v>
+        <v>0.8673785593476091</v>
       </c>
       <c r="D13" t="n">
-        <v>5.115850683149458</v>
+        <v>0.8313257360117869</v>
       </c>
       <c r="E13" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F13" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.54820891459043</v>
+        <v>3.176583948620945</v>
       </c>
       <c r="D14" t="n">
-        <v>19.32205690230898</v>
+        <v>3.139834246625209</v>
       </c>
       <c r="E14" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F14" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.53927199726635</v>
+        <v>3.500131699555782</v>
       </c>
       <c r="D15" t="n">
-        <v>20.93171130147384</v>
+        <v>3.401403086489498</v>
       </c>
       <c r="E15" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F15" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14.31846651868012</v>
+        <v>2.32675080928552</v>
       </c>
       <c r="D16" t="n">
-        <v>14.07803738691617</v>
+        <v>2.287681075373877</v>
       </c>
       <c r="E16" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F16" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.2712190368363</v>
+        <v>4.431573093485899</v>
       </c>
       <c r="D17" t="n">
-        <v>28.32916462937347</v>
+        <v>4.60348925227319</v>
       </c>
       <c r="E17" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F17" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>17.76214485049325</v>
+        <v>2.886348538205153</v>
       </c>
       <c r="D18" t="n">
-        <v>17.64345369220701</v>
+        <v>2.867061224983639</v>
       </c>
       <c r="E18" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F18" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>19.0917488276641</v>
+        <v>3.102409184495416</v>
       </c>
       <c r="D19" t="n">
-        <v>20.41079062049448</v>
+        <v>3.316753475830353</v>
       </c>
       <c r="E19" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F19" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>21.81250626067361</v>
+        <v>3.544532267359461</v>
       </c>
       <c r="D20" t="n">
-        <v>21.62696153012758</v>
+        <v>3.514381248645733</v>
       </c>
       <c r="E20" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F20" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>35.61156656859381</v>
+        <v>5.786879567396494</v>
       </c>
       <c r="D21" t="n">
-        <v>39.82420670449955</v>
+        <v>6.471433589481178</v>
       </c>
       <c r="E21" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F21" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>54.12468291695692</v>
+        <v>8.795260974005499</v>
       </c>
       <c r="D22" t="n">
-        <v>55.6138958976377</v>
+        <v>9.037258083366126</v>
       </c>
       <c r="E22" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F22" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>40.53966255830415</v>
+        <v>6.587695165724424</v>
       </c>
       <c r="D23" t="n">
-        <v>40.03516348568726</v>
+        <v>6.505714066424179</v>
       </c>
       <c r="E23" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F23" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>26.78480851242547</v>
+        <v>4.352531383269139</v>
       </c>
       <c r="D24" t="n">
-        <v>26.2515458678056</v>
+        <v>4.265876203518411</v>
       </c>
       <c r="E24" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F24" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>61.69658178935217</v>
+        <v>10.02569454076973</v>
       </c>
       <c r="D25" t="n">
-        <v>61.11353606456622</v>
+        <v>9.930949610492011</v>
       </c>
       <c r="E25" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F25" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>29.61621744680426</v>
+        <v>4.812635335105693</v>
       </c>
       <c r="D26" t="n">
-        <v>29.03352342634245</v>
+        <v>4.717947556780649</v>
       </c>
       <c r="E26" t="n">
-        <v>13.69845424084379</v>
+        <v>2.225998814137117</v>
       </c>
       <c r="F26" t="n">
-        <v>14.46421071457464</v>
+        <v>2.350434241118379</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
